--- a/www/download/COUNTRY.CAN.zdW16.xlsx
+++ b/www/download/COUNTRY.CAN.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Canadá</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1.48454955467364</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1.54829199104397</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1.56897939670913</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1.39701680160542</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.29873165409332</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.21096455720812</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.13405686179153</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1.06932772901048</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>1.06056909940265</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1.13781952004519</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1.02992656437351</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>0.988992504007109</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.999010974550012</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1.02948443043801</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10576535264411</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>15.143</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15.303</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15.686</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>16.037</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>16.287</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>16.535</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>16.814</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>17.224</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>17.704</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>16.889</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>17.211</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>17.377</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>17.555</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>17.773</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>18.45</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>13.467</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13.719</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14.065</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>14.389</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14.657</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>14.873</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>15.176</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>15.525</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>16.05</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>15.236</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>15.548</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>15.737</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>15.953</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>16.185</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>16.794</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>26666.831</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>26839.923</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>27343.82</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>27813.608</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>28427.011</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>28745.197</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>29156.508</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>29811.526</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>30502.659</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>28685.386</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>29309.432</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>29536.526</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>30157.455</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>30448.512</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>31622.001</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23762.843</t>
+          <t>24847537255.3067</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>24094.571</t>
+          <t>24271789451.0108</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24531.374</t>
+          <t>24303821076.8178</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24968.62</t>
+          <t>25436897347.7618</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>25608.669</t>
+          <t>26694519584.836</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>25863.386</t>
+          <t>26600976977.3226</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26327.656</t>
+          <t>27150482354.3965</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>26871.221</t>
+          <t>26595675259.5192</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>27635.016</t>
+          <t>26687713698.2178</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>25891.954</t>
+          <t>25175094364.4227</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>26494.092</t>
+          <t>27070197887.1685</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>26772.168</t>
+          <t>29201232217.6822</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>27378.325</t>
+          <t>29782261645.0513</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>27689.923</t>
+          <t>28544072643.7855</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>28745.641</t>
+          <t>29142106509.1065</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12404389775.1503</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12738469595.7964</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13493544073.2519</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>14651290875.8472</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>15739068260.5644</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>16299058912.5013</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>16826578280.6131</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>16365358142.3828</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>15683121296.0907</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>14667509303.5514</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>14406327976.3502</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>15410081450.785</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15575218994.676</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>15586427489.6652</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>15336919002.6377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1153545.24273642</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1177015.70442506</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1158511.63397232</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1075177.58559368</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>973772.90830585</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>856916.678048687</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>775462.281533244</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>680001.935903028</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>634962.142359514</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>681263.206843319</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>621034.084195745</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>597582.091283729</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>583272.508246556</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>570058.711859715</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>596565.329265069</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>105816.693355848</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>104388.134171261</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>106950.002478152</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>117090.8379653</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>131274.275192159</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>143187.295763983</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>152937.49380492</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>174108.229794631</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>193638.823410441</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>168925.056499943</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>191415.039786693</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>205746.912019247</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>207728.527223698</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>206532.373880188</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>216678.06341098</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>225400.453368331</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>216953.649327893</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>218837.920968687</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>249356.419979942</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>288382.000770862</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>310385.126836333</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>334762.994059109</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>367852.756218874</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>402591.42507577</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>347073.016776246</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>412320.871574428</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>474234.428427107</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>472456.576917089</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>450188.754343489</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>461225.322046267</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.915680128627046</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.891480826546932</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.81800821687967</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.704192498229699</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.627076557267673</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.586802412264607</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.564647045937654</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.641957405772211</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.762086479997353</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.765259081426376</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.839059338611021</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.737315152129592</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.757813165218328</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.776540712639902</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.874277421368411</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.48454955467364</t>
+          <t>921.102708498222</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.54829199104397</t>
+          <t>928.540081326006</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.56897939670913</t>
+          <t>959.369470419397</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.39701680160542</t>
+          <t>1018.22552589823</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.29873165409332</t>
+          <t>1073.79658827427</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.21096455720812</t>
+          <t>1095.86994624355</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.13405686179153</t>
+          <t>1108.76598643559</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.06932772901048</t>
+          <t>1054.15107701948</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.06056909940265</t>
+          <t>977.131712017761</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.13781952004519</t>
+          <t>962.668902001019</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.02992656437351</t>
+          <t>926.549620011407</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.988992504007109</t>
+          <t>979.200670884581</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.999010974550012</t>
+          <t>976.311107498332</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.02948443043801</t>
+          <t>963.042243355151</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.10576535264411</t>
+          <t>913.252194918458</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>18533719170.7576</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>18899524912.4627</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>18767188428.6609</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>20763553848.2047</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>23137953273.951</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>23941836725.8971</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>23491316303.3837</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>22625109036.2637</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>21030334283.8401</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>16089278481.6079</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>16144033507.113</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>19010281775.676</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>18254747488.7143</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>18096889571.5754</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>18484309853.1292</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>15631375073.1557</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>15809561042.142</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>15650076189.4768</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>17193938818.8643</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>19329047756.7484</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>19802201365.8879</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>19441496876.8538</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>18944316838.3677</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>18102474065.991</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>13623510231.2457</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>13783517294.9544</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>16474308915.2857</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>15545347096.9344</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.016</t>
+          <t>15079326318.0788</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>15884250215.3723</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>2902344097.60191</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>3089963870.32064</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>3117112239.18408</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>3569615029.34034</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>3808905517.20264</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.033</t>
+          <t>4139635360.00927</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.381</t>
+          <t>4049819426.52988</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.765</t>
+          <t>3680792197.89599</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2927860217.84906</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.893</t>
+          <t>2465768250.36226</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>2360516212.15864</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3.687</t>
+          <t>2535972860.39031</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3.887</t>
+          <t>2709400391.77995</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3.964</t>
+          <t>3017563253.49656</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.906</t>
+          <t>2600059637.75689</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1764.53815509459</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>1756.31576050847</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1744.14158024596</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1735.25230274175</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>1747.14925605506</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>1738.92907422756</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>1734.82742531259</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.642</t>
+          <t>1730.87116771489</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1721.79057892316</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.492</t>
+          <t>1699.36002166406</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.935</t>
+          <t>1703.97973136847</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>1701.18016250324</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>1716.17251810945</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.356</t>
+          <t>1710.88375331249</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.252</t>
+          <t>1711.68796895081</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>1760.98527620156</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>1753.92283427813</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>1743.16037095322</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>1734.34566097255</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>1745.35320160976</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>1738.49181837715</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.236</t>
+          <t>1734.0109333024</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.373</t>
+          <t>1730.81961075424</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1722.91523924512</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1698.43447671122</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1702.96090971773</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>1699.72784947123</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>1717.84073950198</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1713.2049071369</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.676</t>
+          <t>1713.94121083612</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>299214.654278324</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>286159.446490303</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>281255.01046267</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>316422.863432316</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>367863.833555302</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>419456.368918671</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>457133.818006681</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>499655.210388148</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>534117.149118701</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>391494.003747311</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>468866.573210593</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>546676.277887219</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>553353.782913256</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>555105.139361434</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>563511.40529126</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9211867417.11126</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8911317775.01865</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>8536765460.65846</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>8433248231.24282</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>9000399077.83259</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>8384910665.90506</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>8203355642.80224</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7579998736.57618</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7262319721.81099</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5842236966.04411</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6259198762.50014</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7154071095.7724</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>7166091503.07184</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6881489037.52781</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>7434646311.61577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>241106.501183731</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>228759.318677411</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>231720.016745406</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>263851.216961713</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>302406.636672374</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>350459.308724165</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>395898.392834727</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>438892.466077438</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>473658.86365252</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>384603.455012015</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>468414.773860725</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>533606.093872262</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>550773.828660798</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>548944.966407457</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>544629.365029872</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26666.831</t>
+          <t>19799012516.7433</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26839.923</t>
+          <t>19641032282.803</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>27343.82</t>
+          <t>20209129184.6218</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27813.608</t>
+          <t>22099116349.0758</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28427.011</t>
+          <t>24085556767.8703</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>28745.197</t>
+          <t>24628112801.5459</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>29156.508</t>
+          <t>25493737610.7126</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29811.526</t>
+          <t>24928991291.203</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>30502.659</t>
+          <t>23709383895.5942</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>28685.386</t>
+          <t>21344773433.3442</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>29309.432</t>
+          <t>22368937308.7253</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>29536.526</t>
+          <t>25225119324.1458</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>30157.455</t>
+          <t>25234206412.7992</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>30448.512</t>
+          <t>24528311717.593</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>31622.001</t>
+          <t>24552669303.9416</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23762.843</t>
+          <t>58108.153094593</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24094.571</t>
+          <t>57400.1278128928</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>24531.374</t>
+          <t>49534.9937172644</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24968.62</t>
+          <t>52571.646470603</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25608.669</t>
+          <t>65457.1968829278</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>25863.386</t>
+          <t>68997.0601945058</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>26327.656</t>
+          <t>61235.4251719544</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>26871.221</t>
+          <t>60762.7443107103</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>27635.016</t>
+          <t>60458.2854661807</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>25891.954</t>
+          <t>6890.5487352959</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>26494.092</t>
+          <t>451.799349867989</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>26772.168</t>
+          <t>13070.1840149569</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>27378.325</t>
+          <t>2579.95425245811</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>27689.923</t>
+          <t>6160.17295397786</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>28745.641</t>
+          <t>18882.0402613883</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>27957.486</t>
+          <t>-10587145099.6321</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27205.487</t>
+          <t>-10729714507.7843</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>27313.251</t>
+          <t>-11672363723.9633</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28624.388</t>
+          <t>-13665868117.833</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30184.244</t>
+          <t>-15085157690.0377</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>30484.468</t>
+          <t>-16243202135.6408</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>31297.423</t>
+          <t>-17290381967.9104</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>30675.264</t>
+          <t>-17348992554.6268</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>30889.909</t>
+          <t>-16447064173.7833</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>29448.211</t>
+          <t>-15502536467.3001</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>31516.052</t>
+          <t>-16109738546.2252</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>34196.706</t>
+          <t>-18071048228.3734</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>35025.258</t>
+          <t>-18068114909.7274</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>33537.742</t>
+          <t>-17646822680.0652</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>29142.107</t>
+          <t>-17118022992.3258</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>323833.348824478</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>315778.233425717</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>317854.675701881</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>376744.109010741</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>433738.22277051</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>497795.146402095</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>558581.381537095</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>610195.059737732</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>648971.421395438</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>575609.486828108</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>684348.791214944</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>771130.510271527</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>789288.342138565</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>788885.716016092</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>768137.323715559</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11664.947</t>
+          <t>0.225750863732174</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11678.471</t>
+          <t>0.218104982210049</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11877.712</t>
+          <t>0.213798657408975</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11944.459</t>
+          <t>0.21800612925844</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12151.603</t>
+          <t>0.217547563353254</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12271.599</t>
+          <t>0.217789803160994</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>12403.781</t>
+          <t>0.211106670864861</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12587.988</t>
+          <t>0.201422991505096</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12836.283</t>
+          <t>0.193640442299912</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12253.053</t>
+          <t>0.176456254337776</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>12567.016</t>
+          <t>0.188042609701449</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>12668.973</t>
+          <t>0.192261537948386</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>13094.59</t>
+          <t>0.183331137828478</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>13095.118</t>
+          <t>0.180090631259025</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>13690.608</t>
+          <t>0.179429078826843</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>372929.605623793</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>374176.318219081</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>384356.407150279</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>452631.199095672</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>513433.137727278</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>583467.528109265</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>666576.552287597</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>739209.93494322</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>790251.203873445</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>715676.82625622</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>814331.414559818</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>887322.549342821</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>921952.006178532</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>932713.862982814</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>893438.294546591</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>13800.011</t>
+          <t>417515.336436275</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>14087.423</t>
+          <t>420935.549132957</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14955.311</t>
+          <t>432069.481815337</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16222.366</t>
+          <t>508486.940052947</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>17367.914</t>
+          <t>574654.688418547</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18101.283</t>
+          <t>650866.49771912</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18751.059</t>
+          <t>733493.39671692</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>18168.951</t>
+          <t>815539.915204537</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>17520.912</t>
+          <t>869085.676439444</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>16533.468</t>
+          <t>784222.62727675</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16185.977</t>
+          <t>888235.481075485</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>17363.821</t>
+          <t>967793.433541088</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>17599.951</t>
+          <t>1005279.89653504</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>17535.246</t>
+          <t>1016367.1689928</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>15336.919</t>
+          <t>974592.942193483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>72.19</t>
+          <t>1243561.0424159</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>1250506.3519049</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>1297375.86688009</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>53.91</t>
+          <t>1523421.87676619</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>1762105.31904669</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>2032807.62136916</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>2380680.4417531</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>2765310.34839756</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>57.73</t>
+          <t>3050357.62235043</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>2893179.40399061</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>3352555.4521423</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>54.18</t>
+          <t>3687026.91955812</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>3886529.85079441</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>57.91</t>
+          <t>3963632.55681866</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>87.43</t>
+          <t>3906433.68259294</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>527678.31117046</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>543246.666915119</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>555594.096125971</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.212</t>
+          <t>565559.921241453</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>578458.688972981</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>601187.717999918</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>615748.83421561</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>623223.699927526</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>637980.101445323</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>615032.877867165</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>616225.516598357</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>628464.388644642</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>648089.902688781</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>659100.174483242</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>668058.383303337</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>470853.581797621</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>482607.837571621</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>494343.561277891</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>503363.181975857</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>516290.844764256</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>537222.041420247</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>557942.084728489</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>563777.676053856</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>579569.27999488</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>561066.598719915</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>564953.559719808</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>576657.831304171</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>595811.486332675</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>607009.879556881</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>613781.475630824</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>280734.979429071</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>272741.665635771</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>277377.218493769</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>332115.306581426</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>383341.718530417</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>442724.771722158</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>502577.522451585</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>556997.082814236</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>590672.599164847</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>510519.600755383</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>630423.27638966</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>708873.466011343</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>712521.939750484</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>713813.089236296</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>700927.797165801</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>23762843000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>24094571000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>24531374000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>24968620000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>25608669000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>25863386000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>26327656000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>26871221000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>27635016000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>25891954000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>26494092000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>26772168000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>27378325000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>27689923000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>28745641000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>26666830726.5914</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>26839923332.7001</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>27343820198.5812</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>27813607710.351</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>28427010914.3314</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>28745197280.4661</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>29156507763.893</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>29811526203.176</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>30502658518.3738</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>28685386391.8636</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>29309432020.3899</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>29536526083.382</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>30157455185.4049</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>30448511562.1443</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>31622001097.275</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>11664946503.4405</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>11678470593.3175</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>11877711654.7646</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11944459364.3361</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12151603431.3342</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12271599470.2647</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12403780586.7602</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12587987615.5463</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12836283035.7477</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12253053485.4088</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>12567016037.3404</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>12668973393.3321</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>13094590383.918</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>13095118495.1891</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>13690608256.4918</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15143131</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15302796</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15686348</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>16036946</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>16287254</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16534560</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>16814489</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>17223936</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>17704097</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>16889310</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>17210866</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>17377209</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>17555443</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>17772837</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>18449875</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13466891</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13718815</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14065013</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14389043</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14657402</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>14873169</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>15175951</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15524680</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>16050161</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>15236297</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>15548361</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>15737409</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>15953131</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>16184573</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>16793739</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>26666830726.5914</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26839923332.7001</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>27343820198.5812</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>27813607710.351</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>28427010914.3314</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>28745197280.4661</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>29156507763.893</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>29811526203.176</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>30502658518.3738</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>28685386391.8636</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>29309432020.3899</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>29536526083.382</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>30157455185.4049</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>30448511562.1443</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>31622001097.275</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23762843000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>24094571000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>24531374000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>24968620000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>25608669000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25863386000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>26327656000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>26871221000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>27635016000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>25891954000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>26494092000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>26772168000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>27378325000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>27689923000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>28745641000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1365527.96228737</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1355973.66083594</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1380445.23205767</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1627775.44447647</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1860912.53771855</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2119134.07086209</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2388772.49507481</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2642017.00121568</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2809910.53806106</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2492268.703248</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2935496.635278</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3250588.81304</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3340328.28866402</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3356078.11922139</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3252175.04021287</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>698250.313844531</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>693677.223165077</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>709446.68883668</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>840602.261666402</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>957996.441598153</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1093591.28017652</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1236070.94033146</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1372536.99614844</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1459758.27088984</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1294742.235942</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1518658.742901</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1676666.88843</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1717801.83628552</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1730180.25531501</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1675520.77553332</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1561085.4054077</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1601996.66340992</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1691052.7310352</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1693441.83363616</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1759965.52983071</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1815240.33130227</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1942562.42989297</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2073343.43472812</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2157660.15258326</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2310305.30979491</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2325881.25732335</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2372252.75871082</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2529997.16842161</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2600757.41723724</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2722440.20059064</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
